--- a/daily_matches/job_matches_2026-07-08.xlsx
+++ b/daily_matches/job_matches_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, S3, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a2fe76ede4c01b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d1b1575f8a785c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud Architect</t>
+          <t>GenAI / Agentic AI Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cutsforth</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76920144878d961b</t>
+          <t>https://www.indeed.com/viewjob?jk=28adfa916d263f86</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Health100 AI</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f05bc19001fa43b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e9837b40940e11e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Health100 AI</t>
+          <t>Senior Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Tableau, Power BI, Python, SQL</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d9b0a1293f2015</t>
+          <t>https://www.indeed.com/viewjob?jk=56e0ecb5d10c6090</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Internal AI Systems</t>
+          <t>Data Scientist - Traditional and Generative AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DISTI</t>
+          <t>American Red Cross</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f9b17c8d74237f</t>
+          <t>https://www.indeed.com/viewjob?jk=c438df75a81825da</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Smart Warehousing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Copilot, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09661b517b573e97</t>
+          <t>https://www.indeed.com/viewjob?jk=15f94818bca4bdbf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Observability</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, Python</t>
+          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7798608e6c8e6d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c53669e0c3539c2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- AI Enablement</t>
+          <t>Campus Intern DTAI Track – Data, Tech &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Health Catalyst</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe3f50110283c78</t>
+          <t>https://www.indeed.com/viewjob?jk=0887e02c88d6f0f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a78dbf7c446b6db</t>
+          <t>https://www.indeed.com/viewjob?jk=7543c33f78de14f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5e4db31e26c352</t>
+          <t>https://www.indeed.com/viewjob?jk=5528172bc7cb59ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Development Environment Engineer</t>
+          <t>Senior Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Dorleco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, LangChain, MLflow, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37c07b878bf682f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b452804964777c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Relevance Engineer â€“ Enterprise Search &amp; AI North Carolina Hybrid</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, Kubernetes, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8895f8575e852d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbce5aa1bf1132d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer. Software Engineering-1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Vanta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Terraform, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebf9b184915ad4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7cf91b1b0e6062</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Scientist</t>
+          <t>AI Engineer - NJ/ Dallas/ Atlanta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160ed09cf6886c46</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8c384aff9a567c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Software Engineer – Java (AI First)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35674fb556e44dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=66fe84cc5dd7e408</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, Live Streaming Video Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flosports</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd48b1457269a43</t>
+          <t>https://www.indeed.com/viewjob?jk=de5e42049df15e49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 1 (Backend UI and AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec07f9df27cc65f</t>
+          <t>https://www.indeed.com/viewjob?jk=721e94b62a1108a4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Drainage Systems</t>
+          <t>Overwatch Imaging</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hilliard, OH, US USA</t>
+          <t>Hood River, OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, Kafka, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, OpenCV, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fa63afaad1ae0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6314ff0f8e78fba3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Lake Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Imprivata</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Data Lake, Dataflow, Docker, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=752c38d3e6729a37</t>
+          <t>https://www.indeed.com/viewjob?jk=56b35438ae6197f4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jr Data Scientist</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Focus Camera</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a96aaa51b91305</t>
+          <t>https://www.indeed.com/viewjob?jk=960de9bbf7f19e90</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Astrana Health</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monterey Park, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8633dc18eebf9dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=76970c4faed26a56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,462 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063331dddd75d54b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4922b6f5fcc6c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>[Remote] Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53980cdec43ed9b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db92aa655f31f542</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Shipt</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, Docker, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=558a5e20e2ac5d6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63eab71ebd083c66</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Everest Re Group</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Warren, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=413aacfa8eb8977a</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Access Management)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cerby</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d31da1d032a50af</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Generative AI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>C3 AI</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7f5319556e18d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Software Engineer II- Enrichment</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>RevSpring, Inc</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LangChain, BigQuery, Docker, Git, BigQuery, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33e34d78b760f572</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer II- Enrichment</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>RevSpring, Inc</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LangChain, BigQuery, Docker, Git, BigQuery, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6892fef49d24c13</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Test Automation Engineer(Web)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Research Innovations Inc</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Alexandria, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c598a2009dd3b917</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Backend &amp; Machine Learning</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Hume AI</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2619555c26e46a9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, Cloud Gaming - Prescriptive Analytics and Optimization</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3350ce324a5ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=83caed5bc2a3f145</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-08.xlsx
+++ b/daily_matches/job_matches_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,117 +468,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Associate - DevOps Engineer / DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, S3, FastAPI, Docker</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d1b1575f8a785c</t>
+          <t>https://www.indeed.com/viewjob?jk=19e39bb741b6ed38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI / Agentic AI Developer</t>
+          <t>SASE Cloud Software Engineer - AI &amp; Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, AWS SageMaker, GCP Vertex AI</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28adfa916d263f86</t>
+          <t>https://www.indeed.com/viewjob?jk=b986b2351d437bc1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Financial Crimes Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>East West Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e9837b40940e11e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7161aca44a69ea</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Avita Care Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e0ecb5d10c6090</t>
+          <t>https://www.indeed.com/viewjob?jk=6c710d28f7d6fe99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist - Traditional and Generative AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Red Cross</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,602 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c438df75a81825da</t>
+          <t>https://www.indeed.com/viewjob?jk=c79ddc7b9618c2a8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOFTWARE ENGINEER</t>
+          <t>Computer Vision Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smart Warehousing</t>
+          <t>1K Training L.L.C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f94818bca4bdbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c53669e0c3539c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Campus Intern DTAI Track – Data, Tech &amp; AI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0887e02c88d6f0f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7543c33f78de14f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5528172bc7cb59ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist / AI Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dorleco</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Columbus, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, LangChain, MLflow, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b452804964777c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, S3, EC2, Kubernetes, Terraform, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbce5aa1bf1132d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Vanta</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Terraform, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7cf91b1b0e6062</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Engineer - NJ/ Dallas/ Atlanta</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Middletown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8c384aff9a567c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66fe84cc5dd7e408</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Litera</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de5e42049df15e49</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (Backend UI and AI)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Earth City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=721e94b62a1108a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Overwatch Imaging</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Hood River, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, OpenCV, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6314ff0f8e78fba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Lake Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Littleton, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, Dataflow, Docker, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56b35438ae6197f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=960de9bbf7f19e90</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76970c4faed26a56</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83caed5bc2a3f145</t>
+          <t>https://www.indeed.com/viewjob?jk=da881ea49014efb8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-08.xlsx
+++ b/daily_matches/job_matches_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,157 +468,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Associate - DevOps Engineer / DevOps Engineer</t>
+          <t>Senior Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>SRM Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e39bb741b6ed38</t>
+          <t>https://www.indeed.com/viewjob?jk=455751ee86cc598d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SASE Cloud Software Engineer - AI &amp; Backend</t>
+          <t>Senior Google Workspace Integration Engineer (Google Classroom Add-on)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Moneyling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b986b2351d437bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8912d706dfda61a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financial Crimes Data Scientist</t>
+          <t>Senior AI Data Architect / Solution Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>BMC Software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, Docker, Kubernetes, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7161aca44a69ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ad53dc7feb9306b7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avita Care Solutions</t>
+          <t>RFA Engineering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, MongoDB, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c710d28f7d6fe99</t>
+          <t>https://www.indeed.com/viewjob?jk=7354a03d95fbbe7c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer – AI Agents &amp; Harnesses</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79ddc7b9618c2a8</t>
+          <t>https://www.indeed.com/viewjob?jk=732b790b6eec5ad0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Computer Vision Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1K Training L.L.C</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,217 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da881ea49014efb8</t>
+          <t>https://www.indeed.com/viewjob?jk=1dc37251158bc972</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Portfolio BI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, NoSQL, Tableau, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NFI Industries</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Camden, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Synapse, Git, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23d808550935261f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Golfballs.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lafayette, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=533b1d187588889e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Scientist 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=869a04734a88b39f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Appleton, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62136f8d0c746b21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior GTM Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PandaDoc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fa680d61868afb2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-08.xlsx
+++ b/daily_matches/job_matches_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Engineer</t>
+          <t>GenAI / Agentic AI Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SRM Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, CI/CD, Git, PostgreSQL</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455751ee86cc598d</t>
+          <t>https://www.indeed.com/viewjob?jk=c27b5087b5b0685d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Google Workspace Integration Engineer (Google Classroom Add-on)</t>
+          <t>Hadoop Big Data Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Moneyling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8912d706dfda61a</t>
+          <t>https://www.indeed.com/viewjob?jk=57accee44e0ebb15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect / Solution Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BMC Software</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Cortex, Docker, Kubernetes, CI/CD, Snowflake</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, MongoDB, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad53dc7feb9306b7</t>
+          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RFA Engineering</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, PySpark, MongoDB, Tableau, Python, SQL, R</t>
+          <t>Generative AI, RAG, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7354a03d95fbbe7c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Agents &amp; Harnesses</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Cortex, AWS SageMaker, S3, Glue, Athena, Redshift, Data Lake, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=732b790b6eec5ad0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Intern - Software Engineer, AI User Experience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Rakuten Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dc37251158bc972</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b4846ad12e6215</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CI/CD, Git, NoSQL, Tableau, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NFI Industries</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Synapse, Git, PySpark, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Docker, AKS, CI/CD, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d808550935261f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Golfballs.com</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533b1d187588889e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae7a2dd93d0c527</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Scientist 2</t>
+          <t>Sr Software Engineer - Remote or Hybrid in MN and DC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Keras, CI/CD, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,77 +811,672 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869a04734a88b39f</t>
+          <t>https://www.indeed.com/viewjob?jk=26d34b22580954e0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62136f8d0c746b21</t>
+          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior GTM Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>EvenUp</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dd446bc5be20fae</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Koalafi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, MLflow, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2389cce7073dab93</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Koalafi</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, MLflow, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bad433435f088d32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr. Java Developer (FTE / Hybrid / Onsite Interview)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45d725c07197007a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SaaS Web Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stanbridge University</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8300e3aac4c8ac41</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kustomer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Terraform, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=227b74cd0b52305c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Interns for AI/ML development</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Navisoft</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f2811776c9f6c55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Meijer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, TensorFlow, PyTorch, Azure ML, Synapse, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dcf2dba583082e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Modeler</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Teleflora</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcb3d2a98d23848f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ideas2it technology pvt lmt</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a960e3778231334</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>American Bible Society</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=963db30c49908c59</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineer, DevOps</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CS Disco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d546dc2d767631ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CS Disco</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11fad1bf8ad4b215</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Engineer - Automotive AI Systems</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07daa87a3fff55a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Healthcare Claims, Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Healthfirst</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Redshift, NoSQL, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc069e016dc89e93</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>React Web Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Python, SQL, R, Bayesian, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa680d61868afb2</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ddad53c4b42fc1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Infrastructure Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>THUMBWAR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4961d3574e6ad023</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-08.xlsx
+++ b/daily_matches/job_matches_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI / Agentic AI Developer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, AWS SageMaker, GCP Vertex AI</t>
+          <t>RAG, Prompt Engineering, S3, BigQuery, CI/CD, GitHub Actions, Git, Databricks, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27b5087b5b0685d</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Big Data Developer</t>
+          <t>Software Engineer II (AI, Python, Typescript)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57accee44e0ebb15</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d7e4de35aac430</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Intern - Software Engineer, AI User Experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Rakuten International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, MongoDB, NoSQL, Tableau</t>
+          <t>LangChain, RAG, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
+          <t>https://www.indeed.com/viewjob?jk=8efb44256648bab2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, S3, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
+          <t>https://www.indeed.com/viewjob?jk=91231705e8648cc9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>(USA) Data Scientist III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cortex, AWS SageMaker, S3, Glue, Athena, Redshift, Data Lake, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, TensorFlow, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=887ce8c182ec4974</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Intern - Software Engineer, AI User Experience</t>
+          <t>Senior Engineer-GenAI Platform Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rakuten Global</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b4846ad12e6215</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dc470ba1b53f34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paperless Parts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
+          <t>https://www.indeed.com/viewjob?jk=084c2ec20628e538</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>MOEV Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, AKS, CI/CD, Git, Kafka, Python, SQL, R</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e06d75873ecb75da</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer P2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae7a2dd93d0c527</t>
+          <t>https://www.indeed.com/viewjob?jk=6372c2f7bdaa2685</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Remote or Hybrid in MN and DC</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d34b22580954e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf893a5e96db4e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, Copilot, Git, Python, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cdcfa6098745a3d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr Digital Tech Support Engr</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EvenUp</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python</t>
+          <t>Data Scientist, RAG, Copilot, Git, Python, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd446bc5be20fae</t>
+          <t>https://www.indeed.com/viewjob?jk=ecd2d9a4e477643c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Koalafi</t>
+          <t>Amplifi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, MLflow, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2389cce7073dab93</t>
+          <t>https://www.indeed.com/viewjob?jk=0585790d77b615f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Koalafi</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, MLflow, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad433435f088d32</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c70cd963a3c6ec</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Java Developer (FTE / Hybrid / Onsite Interview)</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d725c07197007a</t>
+          <t>https://www.indeed.com/viewjob?jk=133737e6d52a581f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SaaS Web Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stanbridge University</t>
+          <t>Holtec International</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, Git, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8300e3aac4c8ac41</t>
+          <t>https://www.indeed.com/viewjob?jk=84ebb4cb215eabb2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (SRE)</t>
+          <t>AI Enablement &amp; Deployment Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kustomer</t>
+          <t>Mattson Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Terraform, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Git, Tableau, Power BI, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=227b74cd0b52305c</t>
+          <t>https://www.indeed.com/viewjob?jk=7280f83e61ea9a18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Interns for AI/ML development</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Navisoft</t>
+          <t>Consumers Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jackson, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Git, Databricks, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,392 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f2811776c9f6c55</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Meijer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Copilot, TensorFlow, PyTorch, Azure ML, Synapse, Databricks, PySpark, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcf2dba583082e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Modeler</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Teleflora</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb3d2a98d23848f</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ideas2it technology pvt lmt</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a960e3778231334</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>American Bible Society</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, S3, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=963db30c49908c59</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Engineer, DevOps</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CS Disco</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d546dc2d767631ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CS Disco</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11fad1bf8ad4b215</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Engineer - Automotive AI Systems</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Stellantis</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Auburn Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07daa87a3fff55a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Healthcare Claims, Data Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Healthfirst</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, NoSQL, Tableau, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc069e016dc89e93</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>React Web Developer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddad53c4b42fc1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Infrastructure Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>THUMBWAR</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4961d3574e6ad023</t>
+          <t>https://www.indeed.com/viewjob?jk=68524532856f1da8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-08.xlsx
+++ b/daily_matches/job_matches_2026-07-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>AI Enterprise Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, BigQuery, CI/CD, GitHub Actions, Git, Databricks, BigQuery, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf6ebaa193170fe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II (AI, Python, Typescript)</t>
+          <t>Part-Time Universal Banker (20 Hours), Sherman Oaks Branch</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d7e4de35aac430</t>
+          <t>https://www.indeed.com/viewjob?jk=dac483d125ca99a4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Intern - Software Engineer, AI User Experience</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rakuten International</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>Pinecone, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efb44256648bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Software Engineer II (AWS, Node)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, S3, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91231705e8648cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc1f6b8eb38b31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(USA) Data Scientist III</t>
+          <t>Senior Data Scientist (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>LG Energy Solution Michigan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Westborough, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Git, Snowflake, Databricks, Polars, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887ce8c182ec4974</t>
+          <t>https://www.indeed.com/viewjob?jk=8866a7feb2242432</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer-GenAI Platform Engineering</t>
+          <t>Site Reliability Engineer- AI Enablement</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Health Catalyst</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc470ba1b53f34</t>
+          <t>https://www.indeed.com/viewjob?jk=93bddf49e5236883</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paperless Parts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, Terraform, Python, R, Scala</t>
+          <t>Hugging Face, FAISS, FastAPI, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084c2ec20628e538</t>
+          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer, ML Engineering (Databricks)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOEV Inc.</t>
+          <t>Curinos</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, CI/CD, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, Copilot, MLflow, CI/CD, Jenkins, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06d75873ecb75da</t>
+          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer P2</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6372c2f7bdaa2685</t>
+          <t>https://www.indeed.com/viewjob?jk=a5357b2479c3349f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Developer - (RAG, Python, Javascript, Google Cloud Platform(GCP))</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cf893a5e96db4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=71fcbf4dc5e9181e</t>
         </is>
       </c>
     </row>
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ritchie Bros.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Python, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcfa6098745a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccfb63f05a4e331</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Digital Tech Support Engr</t>
+          <t>Cloud Data Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Python, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecd2d9a4e477643c</t>
+          <t>https://www.indeed.com/viewjob?jk=e889e3c64d0786f9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GenAI Engineer-Middletown NJ, Atlanta GA, Dallas TX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amplifi</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Middletown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0585790d77b615f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0f1b1c442982b23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c70cd963a3c6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae9d749d311d809</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133737e6d52a581f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c43feead1836daf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Holtec International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, Git, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ebb4cb215eabb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8883e9946b234da5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Enablement &amp; Deployment Analyst</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mattson Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Git, Tableau, Power BI, R, Optimization</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,357 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7280f83e61ea9a18</t>
+          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Consumers Energy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jackson, MI, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer/ AI Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chester Springs, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f75ee8c05bc74bd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Founding Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLERA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MySQL, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=029f889ef83e5c17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Allen Control Systems</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b91e3e0b2b30ade5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Google Advanced Cloud Generative AI Developer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Universal Technologies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6eb381408b55173c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Git, Databricks, NoSQL, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68524532856f1da8</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a797337ae7a7a5f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586f08963185ce12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jr. Data Scientist, Business Analytics &amp; Research</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Universal City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3530bbc78403352</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate/I/II</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Federal Reserve Bank of Cleveland</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, Git, Databricks, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c19c3b99f7215a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GBM - Quantitative Dev/Strat - Systematic Rates Trading, New York</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09a87744fd586630</t>
         </is>
       </c>
     </row>
